--- a/Sample_Data/Machines.xlsx
+++ b/Sample_Data/Machines.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="72">
   <si>
     <t>machine_ID INT (PK)</t>
   </si>
@@ -152,6 +152,81 @@
   </si>
   <si>
     <t>SN-CSC-4422J</t>
+  </si>
+  <si>
+    <t>SN-DLX-8836A</t>
+  </si>
+  <si>
+    <t>SN-WOW-1105B</t>
+  </si>
+  <si>
+    <t>SN-ZBR-9946C</t>
+  </si>
+  <si>
+    <t>SN-PHL-3322D</t>
+  </si>
+  <si>
+    <t>SN-LNV-5542E</t>
+  </si>
+  <si>
+    <t>SN-GEH-7743F</t>
+  </si>
+  <si>
+    <t>SN-BRC-2220G</t>
+  </si>
+  <si>
+    <t>SN-APP-6622H</t>
+  </si>
+  <si>
+    <t>SN-LNV-5589E</t>
+  </si>
+  <si>
+    <t>SN-CSC-4412J</t>
+  </si>
+  <si>
+    <t>SN-OMN-9912K</t>
+  </si>
+  <si>
+    <t>SN-ZBR-9947C</t>
+  </si>
+  <si>
+    <t>SN-DLX-9998Z</t>
+  </si>
+  <si>
+    <t>SN-LNV-5600E</t>
+  </si>
+  <si>
+    <t>SN-APP-6634H</t>
+  </si>
+  <si>
+    <t>SN-DLX-2213L</t>
+  </si>
+  <si>
+    <t>SN-HPL-1102M</t>
+  </si>
+  <si>
+    <t>SN-CSC-4423J</t>
+  </si>
+  <si>
+    <t>SN-DLX-8837A</t>
+  </si>
+  <si>
+    <t>SN-WOW-1106B</t>
+  </si>
+  <si>
+    <t>SN-PHL-3323D</t>
+  </si>
+  <si>
+    <t>SN-LNV-5543E</t>
+  </si>
+  <si>
+    <t>SN-BRC-2221G</t>
+  </si>
+  <si>
+    <t>SN-APP-6623H</t>
+  </si>
+  <si>
+    <t>SN-OMN-9913K</t>
   </si>
 </sst>
 </file>
@@ -788,6 +863,356 @@
         <v>8.0</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="2">
+        <v>26.0</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D27" s="2">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2">
+        <v>27.0</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D28" s="2">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2">
+        <v>28.0</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D29" s="2">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2">
+        <v>29.0</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D30" s="2">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2">
+        <v>30.0</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D31" s="2">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2">
+        <v>31.0</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D32" s="2">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2">
+        <v>32.0</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D33" s="2">
+        <v>7.0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2">
+        <v>33.0</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D34" s="2">
+        <v>8.0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2">
+        <v>34.0</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D35" s="2">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2">
+        <v>35.0</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D36" s="2">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2">
+        <v>36.0</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D37" s="2">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2">
+        <v>37.0</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D38" s="2">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2">
+        <v>38.0</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D39" s="2">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2">
+        <v>39.0</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D40" s="2">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2">
+        <v>40.0</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D41" s="2">
+        <v>7.0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2">
+        <v>41.0</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D42" s="2">
+        <v>8.0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2">
+        <v>42.0</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D43" s="2">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2">
+        <v>43.0</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D44" s="2">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2">
+        <v>44.0</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D45" s="2">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2">
+        <v>45.0</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D46" s="2">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2">
+        <v>46.0</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D47" s="2">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2">
+        <v>47.0</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D48" s="2">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2">
+        <v>48.0</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D49" s="2">
+        <v>7.0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2">
+        <v>49.0</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D50" s="2">
+        <v>8.0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2">
+        <v>50.0</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D51" s="2">
+        <v>1.0</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
